--- a/www/ig/fhir/annuaire/1.2.0-snapshot-1/StructureDefinition-as-dr-healthcareservice-social-equipment.xlsx
+++ b/www/ig/fhir/annuaire/1.2.0-snapshot-1/StructureDefinition-as-dr-healthcareservice-social-equipment.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.0-snapshot-1</t>
+    <t>1.2.0-snapshot-2</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-16T14:13:23+00:00</t>
+    <t>2026-06-19T14:20:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -114,7 +114,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-healthcareservice-social-equipment|1.2.0-snapshot-1</t>
+    <t>https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-healthcareservice-social-equipment|1.2.0-snapshot-2</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -382,7 +382,7 @@
     <t>as-ext-data-trace</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-data-trace|1.2.0-snapshot-1}
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-data-trace|1.2.0-snapshot-2}
 </t>
   </si>
   <si>
@@ -481,7 +481,7 @@
     <t>as-dr-canonical</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-dr-healthcareservice-social-equipment|1.2.0-snapshot-1</t>
+    <t>https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-dr-healthcareservice-social-equipment|1.2.0-snapshot-2</t>
   </si>
   <si>
     <t>HealthcareService.meta.security</t>
@@ -649,7 +649,7 @@
     <t>as-ext-authorization</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-authorization|1.2.0-snapshot-1}
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-authorization|1.2.0-snapshot-2}
 </t>
   </si>
   <si>
@@ -891,7 +891,7 @@
     <t>as-ext-installation</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-installation|1.2.0-snapshot-1}
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-installation|1.2.0-snapshot-2}
 </t>
   </si>
   <si>
@@ -985,7 +985,7 @@
     <t>as-ext-patient-type</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-patient-type|1.2.0-snapshot-1}
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-patient-type|1.2.0-snapshot-2}
 </t>
   </si>
   <si>
@@ -1123,7 +1123,7 @@
     <t>as-ext-supported-capacity</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-supported-capacity|1.2.0-snapshot-1}
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-supported-capacity|1.2.0-snapshot-2}
 </t>
   </si>
   <si>
@@ -1568,7 +1568,7 @@
     <t>HealthcareService.providedBy</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-organization|2.1.0|https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-organization|1.2.0-snapshot-1)
+    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-organization|2.2.0|https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-organization|1.2.0-snapshot-2)
 </t>
   </si>
   <si>

--- a/www/ig/fhir/annuaire/1.2.0-snapshot-1/StructureDefinition-as-dr-healthcareservice-social-equipment.xlsx
+++ b/www/ig/fhir/annuaire/1.2.0-snapshot-1/StructureDefinition-as-dr-healthcareservice-social-equipment.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.0-snapshot-2</t>
+    <t>1.2.0-snapshot-1</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-19T14:20:56+00:00</t>
+    <t>2026-06-16T14:13:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -114,7 +114,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-healthcareservice-social-equipment|1.2.0-snapshot-2</t>
+    <t>https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-healthcareservice-social-equipment|1.2.0-snapshot-1</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -382,7 +382,7 @@
     <t>as-ext-data-trace</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-data-trace|1.2.0-snapshot-2}
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-data-trace|1.2.0-snapshot-1}
 </t>
   </si>
   <si>
@@ -481,7 +481,7 @@
     <t>as-dr-canonical</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-dr-healthcareservice-social-equipment|1.2.0-snapshot-2</t>
+    <t>https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-dr-healthcareservice-social-equipment|1.2.0-snapshot-1</t>
   </si>
   <si>
     <t>HealthcareService.meta.security</t>
@@ -649,7 +649,7 @@
     <t>as-ext-authorization</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-authorization|1.2.0-snapshot-2}
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-authorization|1.2.0-snapshot-1}
 </t>
   </si>
   <si>
@@ -891,7 +891,7 @@
     <t>as-ext-installation</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-installation|1.2.0-snapshot-2}
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-installation|1.2.0-snapshot-1}
 </t>
   </si>
   <si>
@@ -985,7 +985,7 @@
     <t>as-ext-patient-type</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-patient-type|1.2.0-snapshot-2}
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-patient-type|1.2.0-snapshot-1}
 </t>
   </si>
   <si>
@@ -1123,7 +1123,7 @@
     <t>as-ext-supported-capacity</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-supported-capacity|1.2.0-snapshot-2}
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-supported-capacity|1.2.0-snapshot-1}
 </t>
   </si>
   <si>
@@ -1568,7 +1568,7 @@
     <t>HealthcareService.providedBy</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-organization|2.2.0|https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-organization|1.2.0-snapshot-2)
+    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-organization|2.1.0|https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-organization|1.2.0-snapshot-1)
 </t>
   </si>
   <si>
